--- a/Unity/Assets/Config/Excel/PetBarConfig.xlsx
+++ b/Unity/Assets/Config/Excel/PetBarConfig.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE41F31-FDEF-4391-91DD-A9EA1C4D9209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="21495" windowHeight="12045"/>
   </bookViews>
   <sheets>
     <sheet name="PetBarProto" sheetId="1" r:id="rId1"/>
@@ -33,24 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="31">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
-  </si>
-  <si>
-    <t>技能栏名字</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>升级消耗</t>
-  </si>
-  <si>
-    <t>激活技能</t>
-  </si>
-  <si>
-    <t>额外属性</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,13 +50,34 @@
     <t>AddProperty</t>
   </si>
   <si>
+    <t>##type</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>int[]</t>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>技能栏名字</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>升级消耗</t>
+  </si>
+  <si>
+    <t>激活技能</t>
+  </si>
+  <si>
+    <t>额外属性</t>
   </si>
   <si>
     <t>攻击栏位</t>
@@ -122,8 +125,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -134,7 +143,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -142,51 +156,193 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -213,7 +369,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14993743705557422"/>
+        <fgColor theme="0" tint="-0.149937437055574"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -225,98 +381,269 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79970702230903046"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79970702230903046"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79970702230903046"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79970702230903046"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79970702230903046"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79970702230903046"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79970702230903"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79970702230903"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79970702230903"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79970702230903"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79970702230903"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79970702230903"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="15">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -345,6 +672,21 @@
         <color indexed="9"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="9"/>
+      </left>
+      <right style="thin">
+        <color indexed="9"/>
+      </right>
+      <top style="thin">
+        <color indexed="9"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="9"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -399,263 +741,541 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="58">
+  <cellStyleXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="49" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="58">
-    <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 3" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 3" xfId="18" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 3" xfId="21" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 3" xfId="24" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 3" xfId="27" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 3" xfId="30" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="32" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 3" xfId="33" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 3" xfId="36" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+  <cellStyles count="106">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="常规 2 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="常规 2 3" xfId="39" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="常规 2 3 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="常规 2 3 2 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="常规 2 3 2 2 2" xfId="42" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="常规 2 3 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="常规 2 3 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="常规 2 3 3 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="常规 2 3 4" xfId="46" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="常规 3" xfId="47" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="常规 4" xfId="48" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="常规 5" xfId="49" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="常规 5 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="常规 5 2 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="常规 5 3" xfId="52" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="常规 6" xfId="53" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="注释 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="注释 2 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="注释 2 2 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="注释 2 3" xfId="57" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 1 2" xfId="49"/>
+    <cellStyle name="20% - 强调文字颜色 1 2 2" xfId="50"/>
+    <cellStyle name="20% - 强调文字颜色 1 3" xfId="51"/>
+    <cellStyle name="20% - 强调文字颜色 2 2" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2 3" xfId="54"/>
+    <cellStyle name="20% - 强调文字颜色 3 2" xfId="55"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 3 3" xfId="57"/>
+    <cellStyle name="20% - 强调文字颜色 4 2" xfId="58"/>
+    <cellStyle name="20% - 强调文字颜色 4 2 2" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 4 3" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 5 2" xfId="61"/>
+    <cellStyle name="20% - 强调文字颜色 5 2 2" xfId="62"/>
+    <cellStyle name="20% - 强调文字颜色 5 3" xfId="63"/>
+    <cellStyle name="20% - 强调文字颜色 6 2" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 6 2 2" xfId="65"/>
+    <cellStyle name="20% - 强调文字颜色 6 3" xfId="66"/>
+    <cellStyle name="40% - 强调文字颜色 1 2" xfId="67"/>
+    <cellStyle name="40% - 强调文字颜色 1 2 2" xfId="68"/>
+    <cellStyle name="40% - 强调文字颜色 1 3" xfId="69"/>
+    <cellStyle name="40% - 强调文字颜色 2 2" xfId="70"/>
+    <cellStyle name="40% - 强调文字颜色 2 2 2" xfId="71"/>
+    <cellStyle name="40% - 强调文字颜色 2 3" xfId="72"/>
+    <cellStyle name="40% - 强调文字颜色 3 2" xfId="73"/>
+    <cellStyle name="40% - 强调文字颜色 3 2 2" xfId="74"/>
+    <cellStyle name="40% - 强调文字颜色 3 3" xfId="75"/>
+    <cellStyle name="40% - 强调文字颜色 4 2" xfId="76"/>
+    <cellStyle name="40% - 强调文字颜色 4 2 2" xfId="77"/>
+    <cellStyle name="40% - 强调文字颜色 4 3" xfId="78"/>
+    <cellStyle name="40% - 强调文字颜色 5 2" xfId="79"/>
+    <cellStyle name="40% - 强调文字颜色 5 2 2" xfId="80"/>
+    <cellStyle name="40% - 强调文字颜色 5 3" xfId="81"/>
+    <cellStyle name="40% - 强调文字颜色 6 2" xfId="82"/>
+    <cellStyle name="40% - 强调文字颜色 6 2 2" xfId="83"/>
+    <cellStyle name="40% - 强调文字颜色 6 3" xfId="84"/>
+    <cellStyle name="常规 2" xfId="85"/>
+    <cellStyle name="常规 2 2" xfId="86"/>
+    <cellStyle name="常规 2 3" xfId="87"/>
+    <cellStyle name="常规 2 3 2" xfId="88"/>
+    <cellStyle name="常规 2 3 2 2" xfId="89"/>
+    <cellStyle name="常规 2 3 2 2 2" xfId="90"/>
+    <cellStyle name="常规 2 3 2 3" xfId="91"/>
+    <cellStyle name="常规 2 3 3" xfId="92"/>
+    <cellStyle name="常规 2 3 3 2" xfId="93"/>
+    <cellStyle name="常规 2 3 4" xfId="94"/>
+    <cellStyle name="常规 3" xfId="95"/>
+    <cellStyle name="常规 4" xfId="96"/>
+    <cellStyle name="常规 5" xfId="97"/>
+    <cellStyle name="常规 5 2" xfId="98"/>
+    <cellStyle name="常规 5 2 2" xfId="99"/>
+    <cellStyle name="常规 5 3" xfId="100"/>
+    <cellStyle name="常规 6" xfId="101"/>
+    <cellStyle name="注释 2" xfId="102"/>
+    <cellStyle name="注释 2 2" xfId="103"/>
+    <cellStyle name="注释 2 2 2" xfId="104"/>
+    <cellStyle name="注释 2 3" xfId="105"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <colors>
     <indexedColors>
@@ -728,9 +1348,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1801,432 +2418,800 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:GK23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:GJ21"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="11" style="2" customWidth="1"/>
-    <col min="4" max="6" width="14.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="31.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.625" style="3" customWidth="1"/>
-    <col min="9" max="193" width="8.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11" style="1" customWidth="1"/>
+    <col min="3" max="5" width="14.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.625" style="2" customWidth="1"/>
+    <col min="8" max="192" width="8.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" s="1" customFormat="1" ht="14.25">
-      <c r="C1" s="4"/>
-      <c r="H1" s="3"/>
+    <row r="1" customFormat="1" ht="20.1" customHeight="1" spans="1:192">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+      <c r="CM1" s="1"/>
+      <c r="CN1" s="1"/>
+      <c r="CO1" s="1"/>
+      <c r="CP1" s="1"/>
+      <c r="CQ1" s="1"/>
+      <c r="CR1" s="1"/>
+      <c r="CS1" s="1"/>
+      <c r="CT1" s="1"/>
+      <c r="CU1" s="1"/>
+      <c r="CV1" s="1"/>
+      <c r="CW1" s="1"/>
+      <c r="CX1" s="1"/>
+      <c r="CY1" s="1"/>
+      <c r="CZ1" s="1"/>
+      <c r="DA1" s="1"/>
+      <c r="DB1" s="1"/>
+      <c r="DC1" s="1"/>
+      <c r="DD1" s="1"/>
+      <c r="DE1" s="1"/>
+      <c r="DF1" s="1"/>
+      <c r="DG1" s="1"/>
+      <c r="DH1" s="1"/>
+      <c r="DI1" s="1"/>
+      <c r="DJ1" s="1"/>
+      <c r="DK1" s="1"/>
+      <c r="DL1" s="1"/>
+      <c r="DM1" s="1"/>
+      <c r="DN1" s="1"/>
+      <c r="DO1" s="1"/>
+      <c r="DP1" s="1"/>
+      <c r="DQ1" s="1"/>
+      <c r="DR1" s="1"/>
+      <c r="DS1" s="1"/>
+      <c r="DT1" s="1"/>
+      <c r="DU1" s="1"/>
+      <c r="DV1" s="1"/>
+      <c r="DW1" s="1"/>
+      <c r="DX1" s="1"/>
+      <c r="DY1" s="1"/>
+      <c r="DZ1" s="1"/>
+      <c r="EA1" s="1"/>
+      <c r="EB1" s="1"/>
+      <c r="EC1" s="1"/>
+      <c r="ED1" s="1"/>
+      <c r="EE1" s="1"/>
+      <c r="EF1" s="1"/>
+      <c r="EG1" s="1"/>
+      <c r="EH1" s="1"/>
+      <c r="EI1" s="1"/>
+      <c r="EJ1" s="1"/>
+      <c r="EK1" s="1"/>
+      <c r="EL1" s="1"/>
+      <c r="EM1" s="1"/>
+      <c r="EN1" s="1"/>
+      <c r="EO1" s="1"/>
+      <c r="EP1" s="1"/>
+      <c r="EQ1" s="1"/>
+      <c r="ER1" s="1"/>
+      <c r="ES1" s="1"/>
+      <c r="ET1" s="1"/>
+      <c r="EU1" s="1"/>
+      <c r="EV1" s="1"/>
+      <c r="EW1" s="1"/>
+      <c r="EX1" s="1"/>
+      <c r="EY1" s="1"/>
+      <c r="EZ1" s="1"/>
+      <c r="FA1" s="1"/>
+      <c r="FB1" s="1"/>
+      <c r="FC1" s="1"/>
+      <c r="FD1" s="1"/>
+      <c r="FE1" s="1"/>
+      <c r="FF1" s="1"/>
+      <c r="FG1" s="1"/>
+      <c r="FH1" s="1"/>
+      <c r="FI1" s="1"/>
+      <c r="FJ1" s="1"/>
+      <c r="FK1" s="1"/>
+      <c r="FL1" s="1"/>
+      <c r="FM1" s="1"/>
+      <c r="FN1" s="1"/>
+      <c r="FO1" s="1"/>
+      <c r="FP1" s="1"/>
+      <c r="FQ1" s="1"/>
+      <c r="FR1" s="1"/>
+      <c r="FS1" s="1"/>
+      <c r="FT1" s="1"/>
+      <c r="FU1" s="1"/>
+      <c r="FV1" s="1"/>
+      <c r="FW1" s="1"/>
+      <c r="FX1" s="1"/>
+      <c r="FY1" s="1"/>
+      <c r="FZ1" s="1"/>
+      <c r="GA1" s="1"/>
+      <c r="GB1" s="1"/>
+      <c r="GC1" s="1"/>
+      <c r="GD1" s="1"/>
+      <c r="GE1" s="1"/>
+      <c r="GF1" s="1"/>
+      <c r="GG1" s="1"/>
+      <c r="GH1" s="1"/>
+      <c r="GI1" s="1"/>
+      <c r="GJ1" s="1"/>
     </row>
-    <row r="2" spans="3:8" ht="13.5" customHeight="1">
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+    <row r="2" customFormat="1" ht="20.1" customHeight="1" spans="1:192">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+      <c r="CM2" s="1"/>
+      <c r="CN2" s="1"/>
+      <c r="CO2" s="1"/>
+      <c r="CP2" s="1"/>
+      <c r="CQ2" s="1"/>
+      <c r="CR2" s="1"/>
+      <c r="CS2" s="1"/>
+      <c r="CT2" s="1"/>
+      <c r="CU2" s="1"/>
+      <c r="CV2" s="1"/>
+      <c r="CW2" s="1"/>
+      <c r="CX2" s="1"/>
+      <c r="CY2" s="1"/>
+      <c r="CZ2" s="1"/>
+      <c r="DA2" s="1"/>
+      <c r="DB2" s="1"/>
+      <c r="DC2" s="1"/>
+      <c r="DD2" s="1"/>
+      <c r="DE2" s="1"/>
+      <c r="DF2" s="1"/>
+      <c r="DG2" s="1"/>
+      <c r="DH2" s="1"/>
+      <c r="DI2" s="1"/>
+      <c r="DJ2" s="1"/>
+      <c r="DK2" s="1"/>
+      <c r="DL2" s="1"/>
+      <c r="DM2" s="1"/>
+      <c r="DN2" s="1"/>
+      <c r="DO2" s="1"/>
+      <c r="DP2" s="1"/>
+      <c r="DQ2" s="1"/>
+      <c r="DR2" s="1"/>
+      <c r="DS2" s="1"/>
+      <c r="DT2" s="1"/>
+      <c r="DU2" s="1"/>
+      <c r="DV2" s="1"/>
+      <c r="DW2" s="1"/>
+      <c r="DX2" s="1"/>
+      <c r="DY2" s="1"/>
+      <c r="DZ2" s="1"/>
+      <c r="EA2" s="1"/>
+      <c r="EB2" s="1"/>
+      <c r="EC2" s="1"/>
+      <c r="ED2" s="1"/>
+      <c r="EE2" s="1"/>
+      <c r="EF2" s="1"/>
+      <c r="EG2" s="1"/>
+      <c r="EH2" s="1"/>
+      <c r="EI2" s="1"/>
+      <c r="EJ2" s="1"/>
+      <c r="EK2" s="1"/>
+      <c r="EL2" s="1"/>
+      <c r="EM2" s="1"/>
+      <c r="EN2" s="1"/>
+      <c r="EO2" s="1"/>
+      <c r="EP2" s="1"/>
+      <c r="EQ2" s="1"/>
+      <c r="ER2" s="1"/>
+      <c r="ES2" s="1"/>
+      <c r="ET2" s="1"/>
+      <c r="EU2" s="1"/>
+      <c r="EV2" s="1"/>
+      <c r="EW2" s="1"/>
+      <c r="EX2" s="1"/>
+      <c r="EY2" s="1"/>
+      <c r="EZ2" s="1"/>
+      <c r="FA2" s="1"/>
+      <c r="FB2" s="1"/>
+      <c r="FC2" s="1"/>
+      <c r="FD2" s="1"/>
+      <c r="FE2" s="1"/>
+      <c r="FF2" s="1"/>
+      <c r="FG2" s="1"/>
+      <c r="FH2" s="1"/>
+      <c r="FI2" s="1"/>
+      <c r="FJ2" s="1"/>
+      <c r="FK2" s="1"/>
+      <c r="FL2" s="1"/>
+      <c r="FM2" s="1"/>
+      <c r="FN2" s="1"/>
+      <c r="FO2" s="1"/>
+      <c r="FP2" s="1"/>
+      <c r="FQ2" s="1"/>
+      <c r="FR2" s="1"/>
+      <c r="FS2" s="1"/>
+      <c r="FT2" s="1"/>
+      <c r="FU2" s="1"/>
+      <c r="FV2" s="1"/>
+      <c r="FW2" s="1"/>
+      <c r="FX2" s="1"/>
+      <c r="FY2" s="1"/>
+      <c r="FZ2" s="1"/>
+      <c r="GA2" s="1"/>
+      <c r="GB2" s="1"/>
+      <c r="GC2" s="1"/>
+      <c r="GD2" s="1"/>
+      <c r="GE2" s="1"/>
+      <c r="GF2" s="1"/>
+      <c r="GG2" s="1"/>
+      <c r="GH2" s="1"/>
+      <c r="GI2" s="1"/>
+      <c r="GJ2" s="1"/>
     </row>
-    <row r="3" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
+    <row r="3" ht="20.1" customHeight="1" spans="1:7">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="C3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B4" s="8">
+        <v>100001</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="9">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10">
+        <v>2901010</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B5" s="8">
+        <v>100002</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="9">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="E5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2901020</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B6" s="8">
+        <v>100003</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="9">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="E6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="10">
+        <v>2901030</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B7" s="8">
+        <v>100004</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="9">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="E7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="10">
+        <v>2901040</v>
+      </c>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B8" s="8">
+        <v>100005</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="9">
         <v>5</v>
       </c>
+      <c r="E8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="10">
+        <v>2901050</v>
+      </c>
+      <c r="G8" s="11"/>
     </row>
-    <row r="4" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7" t="s">
+    <row r="9" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B9" s="8">
+        <v>100006</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="9">
         <v>6</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="E9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="10">
+        <v>2901060</v>
+      </c>
+      <c r="G9" s="11"/>
     </row>
-    <row r="5" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>12</v>
+    <row r="10" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B10" s="8">
+        <v>200001</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10">
+        <v>2902010</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C6" s="9">
-        <v>100001</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="10">
+    <row r="11" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B11" s="8">
+        <v>200002</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="9">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="10">
+        <v>2902020</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B12" s="8">
+        <v>200003</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="9">
+        <v>3</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="10">
+        <v>2902030</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B13" s="8">
+        <v>200004</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="9">
+        <v>4</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="10">
+        <v>2902040</v>
+      </c>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B14" s="8">
+        <v>200005</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="9">
+        <v>5</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="10">
+        <v>2902050</v>
+      </c>
+      <c r="G14" s="11"/>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B15" s="8">
+        <v>200006</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="9">
+        <v>6</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="10">
+        <v>2902060</v>
+      </c>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B16" s="8">
+        <v>300001</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="9">
         <v>1</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11">
-        <v>2901010</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>15</v>
+      <c r="E16" s="9"/>
+      <c r="F16" s="10">
+        <v>2903010</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="7" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C7" s="9">
-        <v>100002</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="10">
+    <row r="17" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B17" s="8">
+        <v>300002</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="9">
         <v>2</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="11">
-        <v>2901020</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>17</v>
+      <c r="E17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="10">
+        <v>2903020</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C8" s="9">
-        <v>100003</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="10">
+    <row r="18" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B18" s="8">
+        <v>300003</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="9">
         <v>3</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="11">
-        <v>2901030</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>19</v>
+      <c r="E18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="10">
+        <v>2903030</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C9" s="9">
-        <v>100004</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="10">
+    <row r="19" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B19" s="8">
+        <v>300004</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="9">
         <v>4</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="11">
-        <v>2901040</v>
-      </c>
-      <c r="H9" s="12"/>
+      <c r="E19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="8">
+        <v>2903040</v>
+      </c>
+      <c r="G19" s="8"/>
     </row>
-    <row r="10" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C10" s="9">
-        <v>100005</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="10">
+    <row r="20" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B20" s="8">
+        <v>300005</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="9">
         <v>5</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="11">
-        <v>2901050</v>
-      </c>
-      <c r="H10" s="12"/>
+      <c r="E20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="8">
+        <v>2903050</v>
+      </c>
+      <c r="G20" s="8"/>
     </row>
-    <row r="11" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C11" s="9">
-        <v>100006</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="10">
+    <row r="21" ht="20.1" customHeight="1" spans="2:7">
+      <c r="B21" s="8">
+        <v>300006</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="9">
         <v>6</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="11">
-        <v>2901060</v>
-      </c>
-      <c r="H11" s="12"/>
-    </row>
-    <row r="12" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C12" s="9">
-        <v>200001</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="10">
-        <v>1</v>
-      </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11">
-        <v>2902010</v>
-      </c>
-      <c r="H12" s="12" t="s">
+      <c r="E21" s="9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C13" s="9">
-        <v>200002</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="10">
-        <v>2</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="11">
-        <v>2902020</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C14" s="9">
-        <v>200003</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="10">
-        <v>3</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="11">
-        <v>2902030</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C15" s="9">
-        <v>200004</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="10">
-        <v>4</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="11">
-        <v>2902040</v>
-      </c>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C16" s="9">
-        <v>200005</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="10">
-        <v>5</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="11">
-        <v>2902050</v>
-      </c>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C17" s="9">
-        <v>200006</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="10">
-        <v>6</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="11">
-        <v>2902060</v>
-      </c>
-      <c r="H17" s="12"/>
-    </row>
-    <row r="18" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C18" s="9">
-        <v>300001</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="10">
-        <v>1</v>
-      </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11">
-        <v>2903010</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C19" s="9">
-        <v>300002</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="10">
-        <v>2</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="11">
-        <v>2903020</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C20" s="9">
-        <v>300003</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="10">
-        <v>3</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="11">
-        <v>2903030</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C21" s="9">
-        <v>300004</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="10">
-        <v>4</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="9">
-        <v>2903040</v>
-      </c>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C22" s="9">
-        <v>300005</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="10">
-        <v>5</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="9">
-        <v>2903050</v>
-      </c>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="3:8" ht="20.100000000000001" customHeight="1">
-      <c r="C23" s="9">
-        <v>300006</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="10">
-        <v>6</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="9">
+      <c r="F21" s="8">
         <v>2903060</v>
       </c>
-      <c r="H23" s="9"/>
+      <c r="G21" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
